--- a/project/outputs_xlsx_solution/test_new3.4-wide-NC-1.xlsx
+++ b/project/outputs_xlsx_solution/test_new3.4-wide-NC-1.xlsx
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
@@ -1208,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="Q18" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R18" t="s">
         <v>14</v>
@@ -1217,9 +1217,6 @@
         <v>14</v>
       </c>
       <c r="T18" t="s">
-        <v>14</v>
-      </c>
-      <c r="U18" t="s">
         <v>19</v>
       </c>
       <c r="Z18" t="s">
@@ -1283,10 +1280,10 @@
       <c r="Q20" t="s">
         <v>21</v>
       </c>
+      <c r="T20" t="s">
+        <v>14</v>
+      </c>
       <c r="U20" t="s">
-        <v>14</v>
-      </c>
-      <c r="V20" t="s">
         <v>19</v>
       </c>
       <c r="AB20" t="s">
@@ -1310,12 +1307,9 @@
         <v>9</v>
       </c>
       <c r="Q21" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="R21" t="s">
-        <v>14</v>
-      </c>
-      <c r="S21" t="s">
         <v>19</v>
       </c>
       <c r="AC21" t="s">
@@ -1339,12 +1333,9 @@
         <v>9</v>
       </c>
       <c r="R22" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="S22" t="s">
-        <v>14</v>
-      </c>
-      <c r="T22" t="s">
         <v>19</v>
       </c>
       <c r="AD22" t="s">
@@ -1370,10 +1361,10 @@
       <c r="R23" t="s">
         <v>21</v>
       </c>
+      <c r="S23" t="s">
+        <v>14</v>
+      </c>
       <c r="T23" t="s">
-        <v>14</v>
-      </c>
-      <c r="U23" t="s">
         <v>19</v>
       </c>
       <c r="AE23" t="s">
@@ -1399,10 +1390,10 @@
       <c r="R24" t="s">
         <v>21</v>
       </c>
+      <c r="T24" t="s">
+        <v>14</v>
+      </c>
       <c r="U24" t="s">
-        <v>14</v>
-      </c>
-      <c r="V24" t="s">
         <v>19</v>
       </c>
       <c r="AF24" t="s">
@@ -1428,6 +1419,9 @@
       <c r="S25" t="s">
         <v>21</v>
       </c>
+      <c r="T25" t="s">
+        <v>14</v>
+      </c>
       <c r="U25" t="s">
         <v>14</v>
       </c>
@@ -1435,9 +1429,6 @@
         <v>14</v>
       </c>
       <c r="W25" t="s">
-        <v>14</v>
-      </c>
-      <c r="X25" t="s">
         <v>19</v>
       </c>
       <c r="AG25" t="s">
@@ -1504,10 +1495,10 @@
       <c r="T27" t="s">
         <v>21</v>
       </c>
+      <c r="W27" t="s">
+        <v>14</v>
+      </c>
       <c r="X27" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y27" t="s">
         <v>19</v>
       </c>
       <c r="AI27" t="s">
@@ -1531,12 +1522,9 @@
         <v>9</v>
       </c>
       <c r="T28" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="U28" t="s">
-        <v>14</v>
-      </c>
-      <c r="V28" t="s">
         <v>19</v>
       </c>
       <c r="AJ28" t="s">
@@ -1563,12 +1551,9 @@
         <v>27</v>
       </c>
       <c r="U29" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V29" t="s">
-        <v>14</v>
-      </c>
-      <c r="W29" t="s">
         <v>19</v>
       </c>
       <c r="AK29" t="s">
@@ -1595,12 +1580,9 @@
         <v>27</v>
       </c>
       <c r="V30" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W30" t="s">
-        <v>14</v>
-      </c>
-      <c r="X30" t="s">
         <v>19</v>
       </c>
       <c r="AL30" t="s">
@@ -1627,12 +1609,9 @@
         <v>27</v>
       </c>
       <c r="W31" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="X31" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y31" t="s">
         <v>19</v>
       </c>
       <c r="AM31" t="s">
@@ -1659,7 +1638,7 @@
         <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="s">
         <v>14</v>
@@ -1668,9 +1647,6 @@
         <v>14</v>
       </c>
       <c r="AA32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB32" t="s">
         <v>19</v>
       </c>
       <c r="AN32" t="s">
@@ -1740,10 +1716,10 @@
       <c r="Z34" t="s">
         <v>21</v>
       </c>
+      <c r="AA34" t="s">
+        <v>14</v>
+      </c>
       <c r="AB34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC34" t="s">
         <v>19</v>
       </c>
       <c r="AP34" t="s">
@@ -1770,12 +1746,9 @@
         <v>27</v>
       </c>
       <c r="AA35" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AB35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC35" t="s">
         <v>19</v>
       </c>
       <c r="AQ35" t="s">
@@ -1802,12 +1775,9 @@
         <v>27</v>
       </c>
       <c r="AB36" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AC36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD36" t="s">
         <v>19</v>
       </c>
       <c r="AR36" t="s">
@@ -1834,12 +1804,9 @@
         <v>27</v>
       </c>
       <c r="AC37" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AD37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE37" t="s">
         <v>19</v>
       </c>
       <c r="AS37" t="s">
@@ -1866,12 +1833,9 @@
         <v>27</v>
       </c>
       <c r="AD38" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF38" t="s">
         <v>19</v>
       </c>
       <c r="AT38" t="s">
@@ -1898,7 +1862,7 @@
         <v>27</v>
       </c>
       <c r="AE39" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AF39" t="s">
         <v>14</v>
@@ -1907,9 +1871,6 @@
         <v>14</v>
       </c>
       <c r="AH39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI39" t="s">
         <v>19</v>
       </c>
       <c r="AU39" t="s">
@@ -1936,7 +1897,7 @@
         <v>27</v>
       </c>
       <c r="AF40" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AG40" t="s">
         <v>14</v>
@@ -1948,9 +1909,6 @@
         <v>14</v>
       </c>
       <c r="AJ40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK40" t="s">
         <v>19</v>
       </c>
       <c r="AV40" t="s">
@@ -1979,10 +1937,10 @@
       <c r="AG41" t="s">
         <v>21</v>
       </c>
+      <c r="AH41" t="s">
+        <v>14</v>
+      </c>
       <c r="AI41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ41" t="s">
         <v>19</v>
       </c>
       <c r="AW41" t="s">
@@ -2009,12 +1967,9 @@
         <v>27</v>
       </c>
       <c r="AH42" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AI42" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ42" t="s">
         <v>19</v>
       </c>
       <c r="AX42" t="s">
@@ -2041,12 +1996,9 @@
         <v>27</v>
       </c>
       <c r="AI43" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AJ43" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK43" t="s">
         <v>19</v>
       </c>
       <c r="AY43" t="s">
@@ -2073,12 +2025,9 @@
         <v>27</v>
       </c>
       <c r="AJ44" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AK44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL44" t="s">
         <v>19</v>
       </c>
       <c r="AZ44" t="s">
@@ -2105,12 +2054,9 @@
         <v>27</v>
       </c>
       <c r="AK45" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AL45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM45" t="s">
         <v>19</v>
       </c>
       <c r="BA45" t="s">
@@ -2127,25 +2073,22 @@
       <c r="C46" t="s">
         <v>28</v>
       </c>
+      <c r="AL46" t="s">
+        <v>5</v>
+      </c>
       <c r="AM46" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN46" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AO46" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AP46" t="s">
         <v>14</v>
       </c>
       <c r="AQ46" t="s">
-        <v>14</v>
-      </c>
-      <c r="AR46" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS46" t="s">
         <v>19</v>
       </c>
       <c r="BB46" t="s">
@@ -2162,14 +2105,17 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
+      <c r="AL47" t="s">
+        <v>5</v>
+      </c>
       <c r="AM47" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN47" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AO47" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AP47" t="s">
         <v>14</v>
@@ -2178,12 +2124,6 @@
         <v>14</v>
       </c>
       <c r="AR47" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS47" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT47" t="s">
         <v>19</v>
       </c>
       <c r="BC47" t="s">
@@ -2200,19 +2140,19 @@
       <c r="C48" t="s">
         <v>29</v>
       </c>
+      <c r="AL48" t="s">
+        <v>5</v>
+      </c>
       <c r="AM48" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN48" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO48" t="s">
         <v>21</v>
       </c>
-      <c r="AS48" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT48" t="s">
+      <c r="AQ48" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR48" t="s">
         <v>19</v>
       </c>
       <c r="BD48" t="s">
@@ -2229,19 +2169,22 @@
       <c r="C49" t="s">
         <v>30</v>
       </c>
+      <c r="AL49" t="s">
+        <v>5</v>
+      </c>
       <c r="AM49" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN49" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="AO49" t="s">
         <v>21</v>
       </c>
-      <c r="AT49" t="s">
-        <v>14</v>
-      </c>
-      <c r="AU49" t="s">
+      <c r="AR49" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS49" t="s">
         <v>19</v>
       </c>
       <c r="BE49" t="s">
